--- a/output/pdf_financials_xlsx/CLIP.xlsx
+++ b/output/pdf_financials_xlsx/CLIP.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015144</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.05767</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.08949600000000001</v>
       </c>
     </row>
     <row r="13">
@@ -949,13 +949,13 @@
         <v>-5.491946</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-9.316566999999999</v>
+        <v>-9.301423</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-9.316566999999999</v>
+        <v>-9.374237000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-9.338779000000001</v>
+        <v>-9.428274999999999</v>
       </c>
     </row>
     <row r="28">
@@ -987,13 +987,13 @@
         <v>-4.737774</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.694458</v>
+        <v>-7.679314</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.352966</v>
+        <v>-7.410636</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.377085</v>
+        <v>-7.466581</v>
       </c>
     </row>
     <row r="30">
@@ -1006,13 +1006,13 @@
         <v>-195452.7227722772</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-27790.86936107198</v>
+        <v>-27736.17221078484</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1272.317746950697</v>
+        <v>-1282.296654029371</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-312.5474249346166</v>
+        <v>-316.3391318679037</v>
       </c>
     </row>
     <row r="31">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.220247</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.962492</v>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.220247</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.962492</v>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.523709</v>
+        <v>0.303462</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.239361</v>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">

--- a/output/pdf_financials_xlsx/CLIP.xlsx
+++ b/output/pdf_financials_xlsx/CLIP.xlsx
@@ -661,13 +661,13 @@
         <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.850216</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.234925</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.976547</v>
       </c>
     </row>
     <row r="14">
@@ -949,13 +949,13 @@
         <v>-5.491946</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-9.301423</v>
+        <v>-8.451207</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-9.374237000000001</v>
+        <v>-8.139312</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-9.428274999999999</v>
+        <v>-7.451728</v>
       </c>
     </row>
     <row r="28">
@@ -987,13 +987,13 @@
         <v>-4.737774</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.679314</v>
+        <v>-6.829098</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.410636</v>
+        <v>-6.175711</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.466581</v>
+        <v>-5.490034</v>
       </c>
     </row>
     <row r="30">
@@ -1006,13 +1006,13 @@
         <v>-195452.7227722772</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-27736.17221078484</v>
+        <v>-24665.35919384549</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1282.296654029371</v>
+        <v>-1068.611864292401</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-316.3391318679037</v>
+        <v>-232.598104739676</v>
       </c>
     </row>
     <row r="31">
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.754172</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.622109</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.963601</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.961694</v>
       </c>
     </row>
     <row r="101">
@@ -6342,7 +6342,11 @@
           <t>Depreciation of property and equipment 4</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -6376,7 +6380,11 @@
           <t>Depreciation of right-of-use assets 6</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -6412,7 +6420,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7004,7 +7012,11 @@
           <t>Additions to intangible assets 5</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -7608,7 +7620,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -7642,7 +7658,11 @@
           <t>Depreciation of right-of-use assets 7</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -7678,7 +7698,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8176,7 +8196,11 @@
           <t>Additions to intangible assets 6</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -8462,7 +8486,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E151" s="5" t="n">
         <v>0.018351</v>
       </c>
@@ -8496,7 +8524,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>0.449137</v>
       </c>
@@ -8532,7 +8564,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -11666,7 +11698,11 @@
           <t>Net financing expenses $</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -13068,7 +13104,11 @@
           <t>Net financing expenses $</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CLIP.xlsx
+++ b/output/pdf_financials_xlsx/CLIP.xlsx
@@ -1705,13 +1705,13 @@
         <v>0.032032</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.171164</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.180053</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.29259</v>
       </c>
     </row>
     <row r="68">
@@ -1724,13 +1724,13 @@
         <v>1.261201</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.9695279999999999</v>
+        <v>1.140692</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.521068</v>
+        <v>0.701121</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1.275445</v>
+        <v>1.568035</v>
       </c>
     </row>
     <row r="69">
@@ -1762,13 +1762,13 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.64357</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>1.235947</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>1.548138</v>
       </c>
     </row>
     <row r="71">
@@ -1781,13 +1781,13 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.64357</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>1.235947</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>1.548138</v>
       </c>
     </row>
     <row r="72">
@@ -1857,13 +1857,13 @@
         <v>2.632495</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.101693</v>
+        <v>1.286959</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1.926998</v>
+        <v>0.510998</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.129337</v>
+        <v>0.288609</v>
       </c>
     </row>
     <row r="76">
@@ -1953,20 +1953,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>1.470472647842399</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1.457163337801687</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.1950801590794852</v>
       </c>
     </row>
     <row r="81">
@@ -3518,7 +3512,11 @@
           <t>Lease liabilities 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -4526,7 +4524,11 @@
           <t>Lease liabilities 7 1,235,947</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -6526,7 +6528,11 @@
           <t>Deferred tax recovery 20</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
